--- a/artfynd/A 38162-2025 artfynd.xlsx
+++ b/artfynd/A 38162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2231,6 +2231,108 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130782111</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106586</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hisingen, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>322073</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6415383</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Göteborg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rödbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flerstammigt. Mäthöjd: ca 40 cm</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elias Halling</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elias Halling</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38162-2025 artfynd.xlsx
+++ b/artfynd/A 38162-2025 artfynd.xlsx
@@ -2236,7 +2236,7 @@
         <v>130782111</v>
       </c>
       <c r="B15" t="n">
-        <v>106586</v>
+        <v>106599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38162-2025 artfynd.xlsx
+++ b/artfynd/A 38162-2025 artfynd.xlsx
@@ -2236,7 +2236,7 @@
         <v>130782111</v>
       </c>
       <c r="B15" t="n">
-        <v>106599</v>
+        <v>106600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 38162-2025 artfynd.xlsx
+++ b/artfynd/A 38162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2236,7 +2236,7 @@
         <v>130782111</v>
       </c>
       <c r="B15" t="n">
-        <v>106600</v>
+        <v>106603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2332,6 +2332,107 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130842754</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106603</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hisingen, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>321903</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6415314</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Göteborg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rödbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elias Halling</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elias Halling</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Göteborgs Stads artdata</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38162-2025 artfynd.xlsx
+++ b/artfynd/A 38162-2025 artfynd.xlsx
@@ -2236,7 +2236,7 @@
         <v>130782111</v>
       </c>
       <c r="B15" t="n">
-        <v>106603</v>
+        <v>106617</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>130842754</v>
       </c>
       <c r="B16" t="n">
-        <v>106603</v>
+        <v>106617</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 38162-2025 artfynd.xlsx
+++ b/artfynd/A 38162-2025 artfynd.xlsx
@@ -2236,7 +2236,7 @@
         <v>130782111</v>
       </c>
       <c r="B15" t="n">
-        <v>106617</v>
+        <v>106655</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>130842754</v>
       </c>
       <c r="B16" t="n">
-        <v>106617</v>
+        <v>106655</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 38162-2025 artfynd.xlsx
+++ b/artfynd/A 38162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2712506</v>
+        <v>104431409</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>1935</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Vattenstånds</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Jacobaea aquatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hill) G. Gaertn. et al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Oxhagen, Rödbo, Boh</t>
+          <t>L. Oxhagens väg, Ellebovägen, 150 m N om, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>322024.9099231921</v>
+        <v>322043</v>
       </c>
       <c r="R2" t="n">
-        <v>6415426.722816034</v>
+        <v>6415607</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,29 +754,19 @@
           <t>Rödbo</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>OB-Gbg-0179</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett hyfsat stort bestånd har funnits här sedan länge.</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,38 +775,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>lövskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Sören Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Sören Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7288235</v>
+        <v>114750041</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,47 +809,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Oxhagen, Rödbo, Boh</t>
+          <t>Asplunden-Alhaga, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322024.9099231921</v>
+        <v>322021</v>
       </c>
       <c r="R3" t="n">
-        <v>6415426.722816034</v>
+        <v>6415522</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,27 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På död gren av relativt klen ek, i södra delen av angiven lokal.</t>
+          <t>Detta fynd är registrerat under Callunas inventering EEN0070 NVI – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,95 +882,86 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Sumpskog, torplämning</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alexander Schäpers</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Calluna AB: NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7288232</v>
+        <v>83936438</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Oxhagen, Rödbo, Boh</t>
+          <t>Lilla Oxhagen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322024.9099231921</v>
+        <v>322055</v>
       </c>
       <c r="R4" t="n">
-        <v>6415426.722816034</v>
+        <v>6415407</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,22 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,60 +999,51 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Ulf Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Ulf Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91736834</v>
+        <v>92390889</v>
       </c>
       <c r="B5" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1109,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322039.0823409483</v>
+        <v>322055</v>
       </c>
       <c r="R5" t="n">
-        <v>6415385.053891612</v>
+        <v>6415407</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,22 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,27 +1108,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Ulf Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Ulf Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92390889</v>
+        <v>114750039</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,23 +1149,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Oxhagen, Boh</t>
+          <t>Asplunden-Alhaga, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322054.9960075642</v>
+        <v>322055</v>
       </c>
       <c r="R6" t="n">
-        <v>6415406.733966331</v>
+        <v>6415551</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,22 +1185,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Detta fynd är registrerat under Callunas inventering EEN0070 NVI – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,76 +1204,70 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Alexander Schäpers</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Calluna AB: NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91755898</v>
+        <v>114750045</v>
       </c>
       <c r="B7" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220250</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Oxhagen, Boh</t>
+          <t>Asplunden-Alhaga, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322054.9960075642</v>
+        <v>322073</v>
       </c>
       <c r="R7" t="n">
-        <v>6415406.733966331</v>
+        <v>6415512</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,22 +1291,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Detta fynd är registrerat under Callunas inventering EEN0070 NVI – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,51 +1310,49 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Alexander Schäpers</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Calluna AB: NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105725373</v>
+        <v>130782111</v>
       </c>
       <c r="B8" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1452,17 +1363,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RÖDBO: LILLA OXHAGEN, Boh</t>
+          <t>Hisingen, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>322054.9960075642</v>
+        <v>322073</v>
       </c>
       <c r="R8" t="n">
-        <v>6415406.733966331</v>
+        <v>6415383</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,27 +1397,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>Flerstammigt. Mäthöjd: ca 40 cm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,69 +1422,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Elias Halling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
-        </is>
-      </c>
+          <t>Elias Halling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105725372</v>
+        <v>130842754</v>
       </c>
       <c r="B9" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RÖDBO: LILLA OXHAGEN, Boh</t>
+          <t>Hisingen, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>322054.9960075642</v>
+        <v>321903</v>
       </c>
       <c r="R9" t="n">
-        <v>6415406.733966331</v>
+        <v>6415314</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,27 +1499,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,53 +1519,48 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Elias Halling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
+          <t>Elias Halling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
+          <t>Göteborgs Stads artdata</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105725378</v>
+        <v>105725373</v>
       </c>
       <c r="B10" t="n">
-        <v>104505</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221735</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åkerrödtoppa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontites vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bellardi) Dumort.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1698,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>322054.9960075642</v>
+        <v>322055</v>
       </c>
       <c r="R10" t="n">
-        <v>6415406.733966331</v>
+        <v>6415407</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1731,19 +1603,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1779,37 +1641,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105725370</v>
+        <v>105725378</v>
       </c>
       <c r="B11" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107624</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222002</v>
+        <v>221735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Åkerrödtoppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Odontites vernus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bellardi) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1819,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>322054.9960075642</v>
+        <v>322055</v>
       </c>
       <c r="R11" t="n">
-        <v>6415406.733966331</v>
+        <v>6415407</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1852,19 +1709,9 @@
           <t>1920-01-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1900,32 +1747,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114750045</v>
+        <v>105725370</v>
       </c>
       <c r="B12" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>222002</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1936,17 +1778,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Asplunden-Alhaga, Boh</t>
+          <t>RÖDBO: LILLA OXHAGEN, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>322073</v>
+        <v>322055</v>
       </c>
       <c r="R12" t="n">
-        <v>6415512</v>
+        <v>6415407</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1970,17 +1812,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>1920-01-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>1945-12-31</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Detta fynd är registrerat under Callunas inventering EEN0070 NVI – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,31 +1837,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Schäpers</t>
+          <t>Via Mora Aronsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Calluna AB NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
+          <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114750039</v>
+        <v>105725372</v>
       </c>
       <c r="B13" t="n">
-        <v>105292</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,37 +1864,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>223246</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Asplunden-Alhaga, Boh</t>
+          <t>RÖDBO: LILLA OXHAGEN, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>322055</v>
       </c>
       <c r="R13" t="n">
-        <v>6415551</v>
+        <v>6415407</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2081,17 +1918,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>1920-01-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>1945-12-31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Detta fynd är registrerat under Callunas inventering EEN0070 NVI – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2106,331 +1943,17 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Schäpers</t>
+          <t>Via Mora Aronsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Calluna AB NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>114750041</v>
-      </c>
-      <c r="B14" t="n">
-        <v>58078</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>208249</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Rana temporaria</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Asplunden-Alhaga, Boh</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>322021</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6415522</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Göteborg</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Rödbo</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Detta fynd är registrerat under Callunas inventering EEN0070 NVI – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Alexander Schäpers</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Calluna AB NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>130782111</v>
-      </c>
-      <c r="B15" t="n">
-        <v>106689</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Hisingen, Boh</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>322073</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6415383</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Göteborg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Rödbo</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flerstammigt. Mäthöjd: ca 40 cm</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Elias Halling</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Elias Halling</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>130842754</v>
-      </c>
-      <c r="B16" t="n">
-        <v>106690</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Hisingen, Boh</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>321903</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6415314</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Göteborg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Rödbo</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Elias Halling</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Elias Halling</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Göteborgs Stads artdata</t>
+          <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 38162-2025 artfynd.xlsx
+++ b/artfynd/A 38162-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104431409</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
           <t>Calluna AB: NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114750041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83936438</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92390889</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Calluna AB: NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114750039</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
           <t>Calluna AB: NVI EEN0070 – Kraftledningsdragning Göteborg-Ale i Göteborg och Ale kommuner, 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114750045</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130782111</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
           <t>Göteborgs Stads artdata</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130842754</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1638,6 +1683,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105725373</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1744,6 +1794,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105725378</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,6 +1905,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105725370</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,8 +2016,27 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105725372</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>